--- a/BWI/bestwine_output/bestwine_Nigeria.xlsx
+++ b/BWI/bestwine_output/bestwine_Nigeria.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3998,6 +3998,91 @@
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Drinksdirectng</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Drinksdirectng</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>106600</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Lekki</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Lagos, Eti Osa</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>26b Omorinre Johnson Street, Lekki Phase I</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>106104</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.drinksdirect.ng</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>info@drinksdirect.ng</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/drinksdirectng/</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Drinks-Direct-NG-61571689655306/</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/drinksdirectng_/</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCJr8Q0oAgSKYI7kDlGWtbbA</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
